--- a/ig/DM-AVRIL-2025/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
+++ b/ig/DM-AVRIL-2025/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="176">
   <si>
     <t>Property</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250411120000</t>
+    <t>20250415120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-11T12:00:00+01:00</t>
+    <t>2025-04-15T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -222,6 +222,9 @@
   </si>
   <si>
     <t>34875-5</t>
+  </si>
+  <si>
+    <t>34876-3</t>
   </si>
   <si>
     <t>39256-3</t>
@@ -793,7 +796,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E94"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1281,20 +1284,20 @@
         <v>31</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="E37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
         <v>31</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="E38" s="2"/>
     </row>
@@ -1307,7 +1310,7 @@
         <v>31</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="E39" s="2"/>
     </row>
@@ -1320,7 +1323,7 @@
         <v>31</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="E40" s="2"/>
     </row>
@@ -1359,7 +1362,7 @@
         <v>31</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="E43" s="2"/>
     </row>
@@ -1372,7 +1375,7 @@
         <v>31</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="E44" s="2"/>
     </row>
@@ -1385,7 +1388,7 @@
         <v>31</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="E45" s="2"/>
     </row>
@@ -1424,7 +1427,7 @@
         <v>31</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="E48" s="2"/>
     </row>
@@ -1463,7 +1466,7 @@
         <v>31</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="E51" s="2"/>
     </row>
@@ -1476,7 +1479,7 @@
         <v>31</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="E52" s="2"/>
     </row>
@@ -1489,7 +1492,7 @@
         <v>31</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="E53" s="2"/>
     </row>
@@ -1502,7 +1505,7 @@
         <v>31</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E54" s="2"/>
     </row>
@@ -1515,7 +1518,7 @@
         <v>31</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E55" s="2"/>
     </row>
@@ -1528,7 +1531,7 @@
         <v>31</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="E56" s="2"/>
     </row>
@@ -1541,7 +1544,7 @@
         <v>31</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E57" s="2"/>
     </row>
@@ -1554,7 +1557,7 @@
         <v>31</v>
       </c>
       <c r="D58" t="s" s="2">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="E58" s="2"/>
     </row>
@@ -1567,7 +1570,7 @@
         <v>31</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E59" s="2"/>
     </row>
@@ -1580,7 +1583,7 @@
         <v>31</v>
       </c>
       <c r="D60" t="s" s="2">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E60" s="2"/>
     </row>
@@ -1593,7 +1596,7 @@
         <v>31</v>
       </c>
       <c r="D61" t="s" s="2">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E61" s="2"/>
     </row>
@@ -1606,7 +1609,7 @@
         <v>31</v>
       </c>
       <c r="D62" t="s" s="2">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E62" s="2"/>
     </row>
@@ -1619,7 +1622,7 @@
         <v>31</v>
       </c>
       <c r="D63" t="s" s="2">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E63" s="2"/>
     </row>
@@ -1632,20 +1635,20 @@
         <v>31</v>
       </c>
       <c r="D64" t="s" s="2">
-        <v>101</v>
+        <v>48</v>
       </c>
       <c r="E64" s="2"/>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" t="s" s="2">
         <v>31</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>59</v>
+        <v>102</v>
       </c>
       <c r="E65" s="2"/>
     </row>
@@ -1658,7 +1661,7 @@
         <v>31</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="E66" s="2"/>
     </row>
@@ -1723,7 +1726,7 @@
         <v>31</v>
       </c>
       <c r="D71" t="s" s="2">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="E71" s="2"/>
     </row>
@@ -1736,7 +1739,7 @@
         <v>31</v>
       </c>
       <c r="D72" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E72" s="2"/>
     </row>
@@ -1762,7 +1765,7 @@
         <v>31</v>
       </c>
       <c r="D74" t="s" s="2">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E74" s="2"/>
     </row>
@@ -1788,20 +1791,20 @@
         <v>31</v>
       </c>
       <c r="D76" t="s" s="2">
-        <v>114</v>
+        <v>32</v>
       </c>
       <c r="E76" s="2"/>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" t="s" s="2">
         <v>31</v>
       </c>
       <c r="D77" t="s" s="2">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="E77" s="2"/>
     </row>
@@ -1827,7 +1830,7 @@
         <v>31</v>
       </c>
       <c r="D79" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E79" s="2"/>
     </row>
@@ -1853,7 +1856,7 @@
         <v>31</v>
       </c>
       <c r="D81" t="s" s="2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E81" s="2"/>
     </row>
@@ -1866,7 +1869,7 @@
         <v>31</v>
       </c>
       <c r="D82" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E82" s="2"/>
     </row>
@@ -1879,7 +1882,7 @@
         <v>31</v>
       </c>
       <c r="D83" t="s" s="2">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E83" s="2"/>
     </row>
@@ -1905,7 +1908,7 @@
         <v>31</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="E85" s="2"/>
     </row>
@@ -1918,7 +1921,7 @@
         <v>31</v>
       </c>
       <c r="D86" t="s" s="2">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="E86" s="2"/>
     </row>
@@ -1931,7 +1934,7 @@
         <v>31</v>
       </c>
       <c r="D87" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E87" s="2"/>
     </row>
@@ -1944,7 +1947,7 @@
         <v>31</v>
       </c>
       <c r="D88" t="s" s="2">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E88" s="2"/>
     </row>
@@ -1970,7 +1973,7 @@
         <v>31</v>
       </c>
       <c r="D90" t="s" s="2">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="E90" s="2"/>
     </row>
@@ -1983,7 +1986,7 @@
         <v>31</v>
       </c>
       <c r="D91" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E91" s="2"/>
     </row>
@@ -2009,7 +2012,7 @@
         <v>31</v>
       </c>
       <c r="D93" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E93" s="2"/>
     </row>
@@ -2025,6 +2028,19 @@
         <v>34</v>
       </c>
       <c r="E94" s="2"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="B95" s="2"/>
+      <c r="C95" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="D95" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="E95" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -2055,7 +2071,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>28</v>
@@ -2072,72 +2088,72 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>31</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>31</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>31</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>31</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>31</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
@@ -2150,7 +2166,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
@@ -2163,7 +2179,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
@@ -2176,33 +2192,33 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>31</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>31</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
@@ -2215,20 +2231,20 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
         <v>31</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
@@ -2241,7 +2257,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
@@ -2254,7 +2270,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
@@ -2267,7 +2283,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
@@ -2280,7 +2296,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
@@ -2293,7 +2309,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
@@ -2306,7 +2322,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
@@ -2319,7 +2335,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
@@ -2332,20 +2348,20 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
         <v>31</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
@@ -2358,7 +2374,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
@@ -2371,20 +2387,20 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
         <v>31</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -2397,7 +2413,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -2410,20 +2426,20 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
         <v>31</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -2436,7 +2452,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -2449,7 +2465,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
@@ -2462,7 +2478,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -2475,7 +2491,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -2488,7 +2504,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -2501,27 +2517,27 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
         <v>31</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
         <v>31</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E37" s="2"/>
     </row>
@@ -2554,7 +2570,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>28</v>
@@ -2563,7 +2579,7 @@
         <v>28</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>28</v>
@@ -2571,14 +2587,14 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>31</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E3" s="2"/>
     </row>
